--- a/提案資料/WineBank_ワインマイル_PL.xlsx
+++ b/提案資料/WineBank_ワインマイル_PL.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <r>
       <rPr>
@@ -98,7 +98,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">3.5</t>
     </r>
     <r>
       <rPr>
@@ -117,7 +117,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5%</t>
+      <t xml:space="preserve">5.5%</t>
     </r>
     <r>
       <rPr>
@@ -163,37 +163,184 @@
     <t xml:space="preserve">自社在庫の調達コスト</t>
   </si>
   <si>
-    <t xml:space="preserve">保管料・保険料率（年）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時価ベース。管理手数料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の内数</t>
-    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保管料・保険料（円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴与実額。倉持案は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=7,619</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本で年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">210</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均単価（円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ネット最安値ベース。単価が高いほど本数が減り保管料率は下がる</t>
   </si>
   <si>
     <t xml:space="preserve">販売粗利率</t>
@@ -223,7 +370,7 @@
     <t xml:space="preserve">管理手数料率（年）</t>
   </si>
   <si>
-    <t xml:space="preserve">預かり資産に対して</t>
+    <t xml:space="preserve">預かり資産に対して。簿価ベース</t>
   </si>
   <si>
     <t xml:space="preserve">成功報酬率</t>
@@ -244,6 +391,123 @@
     <t xml:space="preserve">販売代金を原資に買い増す額</t>
   </si>
   <si>
+    <t xml:space="preserve">オークション年間回転率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">預かり資産のうち年間で売却される割合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うち当社ルート比率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他ルートでの売却もあるため保守的に半分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">買い手手数料率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">売り手からは取らない。買い手のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保管料率（対 預かり資産）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">← 210</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ 20,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 ＝ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.05%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。従来置いていた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">より軽い</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">■ マイル交換ミックス（どこで使われるかの想定）</t>
   </si>
   <si>
@@ -351,6 +615,18 @@
   </si>
   <si>
     <t xml:space="preserve">手数料の免除。現金流出なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ワインスクール受講料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">講師・会場費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会員交流イベント参加費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会場・飲食費</t>
   </si>
   <si>
     <t xml:space="preserve">ワイン追加購入</t>
@@ -442,7 +718,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">3.5</t>
     </r>
     <r>
       <rPr>
@@ -461,7 +737,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5%</t>
+      <t xml:space="preserve">5.5%</t>
     </r>
     <r>
       <rPr>
@@ -489,26 +765,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">上の実費用（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）の橋渡し</t>
+      <t xml:space="preserve">上の実費用の橋渡し</t>
     </r>
   </si>
   <si>
@@ -659,53 +916,7 @@
     <t xml:space="preserve">会員が受け取る額面（対 販売額）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">会員から見た還元率。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の加重平均</t>
-    </r>
+    <t xml:space="preserve">会員から見た還元率</t>
   </si>
   <si>
     <t xml:space="preserve">マイル原価率（加重平均）</t>
@@ -926,7 +1137,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年目以降＝追加販売なし（ストックのみ）。単位：万円</t>
+      <t xml:space="preserve">年目以降＝追加販売なし。手数料・マイルとも簿価ベース。単位：万円</t>
     </r>
   </si>
   <si>
@@ -993,7 +1204,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">預かり資産 </t>
+      <t xml:space="preserve">預かり資産（簿価）</t>
     </r>
     <r>
       <rPr>
@@ -1082,7 +1293,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">368 × </t>
+      <t xml:space="preserve">418 × </t>
     </r>
     <r>
       <rPr>
@@ -1101,7 +1312,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">44.5%</t>
+      <t xml:space="preserve">43.6%</t>
     </r>
   </si>
   <si>
@@ -1115,42 +1326,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">預かり資産 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1.5%</t>
+      <t xml:space="preserve">本数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×210</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（鈴与実額）</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">　保管料・保険料（自社在庫）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">期末自社在庫 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1.5%</t>
-    </r>
+    <t xml:space="preserve">期末自社在庫にも同率を適用</t>
   </si>
   <si>
     <t xml:space="preserve">　販管費 計</t>
@@ -1159,7 +1361,7 @@
     <t xml:space="preserve">営業利益</t>
   </si>
   <si>
-    <t xml:space="preserve">【営業外費用】</t>
+    <t xml:space="preserve">【営業外】</t>
   </si>
   <si>
     <t xml:space="preserve">　支払利息</t>
@@ -1186,6 +1388,68 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">　オークション収益</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回転率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">当社ルート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50%×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">買い手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">経常利益</t>
   </si>
   <si>
@@ -1232,7 +1496,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">経常利益＋成功報酬発生</t>
+    <t xml:space="preserve">経常利益 ＋ 成功報酬発生</t>
   </si>
   <si>
     <r>
@@ -1274,7 +1538,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（管理手数料 − 保管料）</t>
+      <t xml:space="preserve">（管理手数料 − 保管料 ＋ オークション収益）</t>
     </r>
     <r>
       <rPr>
@@ -1302,26 +1566,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">← 現在の想定原価率と比較してください（前提シート </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
+      <t xml:space="preserve">← 前提シート </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B36 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の想定原価率と比較</t>
     </r>
   </si>
   <si>
@@ -1335,11 +1599,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.00\円"/>
+    <numFmt numFmtId="167" formatCode="#,##0\円"/>
+    <numFmt numFmtId="168" formatCode="0.00\円"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1542,7 +1807,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1587,15 +1852,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1611,15 +1872,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1663,12 +1936,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1691,27 +1960,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1967,12 +2224,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2025,11 +2282,11 @@
         <v>5200</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">D6*E6</f>
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2047,11 +2304,11 @@
         <v>2800</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">D7*E7</f>
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2069,11 +2326,11 @@
         <v>2000</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="F8" s="7" t="n">
         <f aca="false">D8*E8</f>
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2085,17 +2342,17 @@
         <f aca="false">SUM(C6:C8)</f>
         <v>61</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>10000</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">IF(D9=0,0,F9/D9)</f>
-        <v>0.0368</v>
-      </c>
-      <c r="F9" s="12" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <f aca="false">SUM(F6:F8)</f>
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -2107,21 +2364,21 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="14" t="n">
         <v>0.03</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -2129,207 +2386,297 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="15" t="n">
-        <v>0.015</v>
+      <c r="B14" s="16" t="n">
+        <v>210</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>0.3</v>
+      <c r="B15" s="16" t="n">
+        <v>20000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="15" t="n">
-        <v>0.025</v>
+      <c r="B16" s="14" t="n">
+        <v>0.3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>0.25</v>
+      <c r="B17" s="14" t="n">
+        <v>0.025</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>10000</v>
+      <c r="B18" s="14" t="n">
+        <v>0.25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="17" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
+      <c r="A21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="A22" s="13" t="s">
         <v>35</v>
       </c>
+      <c r="B22" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C23" s="18" t="n">
+      <c r="A23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <f aca="false">B14/B15</f>
+        <v>0.0105</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D28" s="8" t="n">
         <v>0.9</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="19" t="n">
-        <f aca="false">SUM(B23:B28)</f>
-        <v>1</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="19" t="n">
-        <f aca="false">SUMPRODUCT(B23:B28,D23:D28)</f>
-        <v>0.445</v>
+      <c r="B29" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0.45</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="12" t="n">
+        <f aca="false">SUM(B28:B35)</f>
+        <v>1</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="21" t="n">
+        <f aca="false">SUMPRODUCT(B28:B35,D28:D35)</f>
+        <v>0.436</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2348,27 +2695,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>50</v>
+      <c r="A1" s="22" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>52</v>
+      <c r="A4" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2379,167 +2726,167 @@
         <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="str">
+      <c r="A6" s="24" t="str">
         <f aca="false">前提!A6</f>
         <v>PRESTIGE</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="25" t="n">
         <f aca="false">前提!D6</f>
         <v>5200</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">前提!E6</f>
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">B6*C6</f>
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="str">
+      <c r="A7" s="24" t="str">
         <f aca="false">前提!A7</f>
         <v>GOLD</v>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="25" t="n">
         <f aca="false">前提!D7</f>
         <v>2800</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">前提!E7</f>
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">B7*C7</f>
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="str">
+      <c r="A8" s="24" t="str">
         <f aca="false">前提!A8</f>
         <v>SIGNATURE</v>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="25" t="n">
         <f aca="false">前提!D8</f>
         <v>2000</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">前提!E8</f>
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">B8*C8</f>
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <f aca="false">SUM(B6:B8)</f>
         <v>10000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="12" t="n">
         <f aca="false">IF(B9=0,0,D9/B9)</f>
-        <v>0.0368</v>
-      </c>
-      <c r="D9" s="12" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <f aca="false">SUM(D6:D8)</f>
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>55</v>
+      <c r="A11" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="str">
-        <f aca="false">前提!A23</f>
+      <c r="A13" s="24" t="str">
+        <f aca="false">前提!A28</f>
         <v>系列レストラン</v>
       </c>
-      <c r="B13" s="24" t="n">
-        <f aca="false">前提!B23</f>
-        <v>0.35</v>
+      <c r="B13" s="26" t="n">
+        <f aca="false">前提!B28</f>
+        <v>0.25</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">$D$9*B13</f>
-        <v>128.8</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">前提!D23</f>
+        <v>104.5</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <f aca="false">前提!D28</f>
         <v>0.9</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">C13*D13</f>
-        <v>115.92</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="str">
-        <f aca="false">前提!A24</f>
+      <c r="A14" s="24" t="str">
+        <f aca="false">前提!A29</f>
         <v>グランメゾン</v>
       </c>
-      <c r="B14" s="24" t="n">
-        <f aca="false">前提!B24</f>
-        <v>0.2</v>
+      <c r="B14" s="26" t="n">
+        <f aca="false">前提!B29</f>
+        <v>0.18</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">$D$9*B14</f>
-        <v>73.6</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <f aca="false">前提!D24</f>
+        <v>75.24</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <f aca="false">前提!D29</f>
         <v>0.45</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">C14*D14</f>
-        <v>33.12</v>
+        <v>33.858</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="str">
-        <f aca="false">前提!A25</f>
+      <c r="A15" s="24" t="str">
+        <f aca="false">前提!A30</f>
         <v>WineBank CLUB 会費充当</v>
       </c>
-      <c r="B15" s="24" t="n">
-        <f aca="false">前提!B25</f>
-        <v>0.15</v>
+      <c r="B15" s="26" t="n">
+        <f aca="false">前提!B30</f>
+        <v>0.12</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">$D$9*B15</f>
-        <v>55.2</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <f aca="false">前提!D25</f>
+        <v>50.16</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <f aca="false">前提!D30</f>
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -2548,20 +2895,20 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="str">
-        <f aca="false">前提!A26</f>
+      <c r="A16" s="24" t="str">
+        <f aca="false">前提!A31</f>
         <v>オークション成約手数料</v>
       </c>
-      <c r="B16" s="24" t="n">
-        <f aca="false">前提!B26</f>
-        <v>0.1</v>
+      <c r="B16" s="26" t="n">
+        <f aca="false">前提!B31</f>
+        <v>0.12</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">$D$9*B16</f>
-        <v>36.8</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <f aca="false">前提!D26</f>
+        <v>50.16</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <f aca="false">前提!D31</f>
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -2570,123 +2917,167 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="str">
-        <f aca="false">前提!A27</f>
-        <v>ワイン追加購入</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <f aca="false">前提!B27</f>
-        <v>0.05</v>
+      <c r="A17" s="24" t="str">
+        <f aca="false">前提!A32</f>
+        <v>ワインスクール受講料</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <f aca="false">前提!B32</f>
+        <v>0.1</v>
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">$D$9*B17</f>
-        <v>18.4</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <f aca="false">前提!D27</f>
-        <v>0.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <f aca="false">前提!D32</f>
+        <v>0.5</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">C17*D17</f>
-        <v>14.72</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="str">
-        <f aca="false">前提!A28</f>
-        <v>失効</v>
-      </c>
-      <c r="B18" s="24" t="n">
-        <f aca="false">前提!B28</f>
-        <v>0.15</v>
+      <c r="A18" s="24" t="str">
+        <f aca="false">前提!A33</f>
+        <v>会員交流イベント参加費</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <f aca="false">前提!B33</f>
+        <v>0.08</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">$D$9*B18</f>
-        <v>55.2</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">前提!D28</f>
-        <v>0</v>
+        <v>33.44</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <f aca="false">前提!D33</f>
+        <v>0.5</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">C18*D18</f>
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="str">
+        <f aca="false">前提!A34</f>
+        <v>ワイン追加購入</v>
+      </c>
+      <c r="B19" s="26" t="n">
+        <f aca="false">前提!B34</f>
+        <v>0.05</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <f aca="false">$D$9*B19</f>
+        <v>20.9</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <f aca="false">前提!D34</f>
+        <v>0.8</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <f aca="false">C19*D19</f>
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="str">
+        <f aca="false">前提!A35</f>
+        <v>失効</v>
+      </c>
+      <c r="B20" s="26" t="n">
+        <f aca="false">前提!B35</f>
+        <v>0.1</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <f aca="false">$D$9*B20</f>
+        <v>41.8</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <f aca="false">前提!D35</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="19" t="n">
-        <f aca="false">SUM(B13:B18)</f>
+      <c r="E20" s="7" t="n">
+        <f aca="false">C20*D20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <f aca="false">SUM(B13:B20)</f>
         <v>1</v>
       </c>
-      <c r="C19" s="12" t="n">
-        <f aca="false">SUM(C13:C18)</f>
-        <v>368</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <f aca="false">IF(C19=0,0,E19/C19)</f>
-        <v>0.445</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <f aca="false">SUM(E13:E18)</f>
-        <v>163.76</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="25" t="n">
+      <c r="C21" s="11" t="n">
+        <f aca="false">SUM(C13:C20)</f>
+        <v>418</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <f aca="false">IF(C21=0,0,E21/C21)</f>
+        <v>0.436</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <f aca="false">SUM(E13:E20)</f>
+        <v>182.248</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="27" t="n">
         <f aca="false">IF(B9=0,0,D9/B9)</f>
-        <v>0.0368</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="25" t="n">
-        <f aca="false">D19</f>
-        <v>0.445</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="27" t="n">
-        <f aca="false">IF(B9=0,0,E19/B9)</f>
-        <v>0.016376</v>
+        <v>0.0418</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="28" t="n">
-        <f aca="false">E19</f>
-        <v>163.76</v>
-      </c>
-      <c r="F25" s="2"/>
+      <c r="A25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="27" t="n">
+        <f aca="false">D21</f>
+        <v>0.436</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="29" t="n">
+        <f aca="false">IF(B9=0,0,E21/B9)</f>
+        <v>0.0182248</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="30" t="n">
+        <f aca="false">E21</f>
+        <v>182.248</v>
+      </c>
+      <c r="F27" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2704,306 +3095,314 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>68</v>
+      <c r="A1" s="22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>71</v>
+        <v>84</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="A5" s="32" t="s">
+        <v>86</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="A6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="33" t="n">
         <f aca="false">前提!D9</f>
         <v>10000</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>74</v>
+      <c r="E6" s="15" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="32" t="n">
-        <f aca="false">前提!D9*前提!B16</f>
+      <c r="A7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="33" t="n">
+        <f aca="false">前提!D9*前提!B17</f>
         <v>250</v>
       </c>
-      <c r="C7" s="32" t="n">
-        <f aca="false">前提!D9*前提!B16</f>
+      <c r="C7" s="33" t="n">
+        <f aca="false">前提!D9*前提!B17</f>
         <v>250</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="33" t="n">
+        <v>91</v>
+      </c>
+      <c r="B8" s="34" t="n">
         <f aca="false">SUM(B6:B7)</f>
         <v>10250</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="34" t="n">
         <f aca="false">SUM(C6:C7)</f>
         <v>250</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="A9" s="32" t="s">
+        <v>92</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="32" t="n">
-        <f aca="false">-B6*(1-前提!B15)</f>
+      <c r="A10" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="33" t="n">
+        <f aca="false">-B6*(1-前提!B16)</f>
         <v>-7000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="B11" s="34" t="n">
         <f aca="false">B8+B10</f>
         <v>3250</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <f aca="false">C8+C10</f>
         <v>250</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
+      <c r="A12" s="32" t="s">
+        <v>96</v>
+      </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="32" t="n">
-        <f aca="false">-マイル計算!E19</f>
-        <v>-163.76</v>
-      </c>
-      <c r="C13" s="32" t="n">
-        <f aca="false">-マイル計算!E19</f>
-        <v>-163.76</v>
+      <c r="A13" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <f aca="false">-マイル計算!E21</f>
+        <v>-182.248</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <f aca="false">-マイル計算!E21</f>
+        <v>-182.248</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="32" t="n">
-        <f aca="false">-前提!D9*前提!B14</f>
-        <v>-150</v>
-      </c>
-      <c r="C14" s="32" t="n">
-        <f aca="false">-前提!D9*前提!B14</f>
-        <v>-150</v>
+      <c r="A14" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <f aca="false">-前提!D9*前提!B14/前提!B15</f>
+        <v>-105</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <f aca="false">-前提!D9*前提!B14/前提!B15</f>
+        <v>-105</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="32" t="n">
-        <f aca="false">-(前提!B18+前提!B19-B6*(1-前提!B15))*前提!B14</f>
-        <v>-225</v>
-      </c>
-      <c r="C15" s="32" t="n">
+      <c r="A15" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="33" t="n">
+        <f aca="false">-(前提!B19+前提!B20+B10)*前提!B14/前提!B15</f>
+        <v>-157.5</v>
+      </c>
+      <c r="C15" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="33" t="n">
+        <v>103</v>
+      </c>
+      <c r="B16" s="34" t="n">
         <f aca="false">SUM(B13:B15)</f>
-        <v>-538.76</v>
-      </c>
-      <c r="C16" s="33" t="n">
+        <v>-444.748</v>
+      </c>
+      <c r="C16" s="34" t="n">
         <f aca="false">SUM(C13:C15)</f>
-        <v>-313.76</v>
+        <v>-287.248</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="34" t="n">
+        <v>104</v>
+      </c>
+      <c r="B17" s="35" t="n">
         <f aca="false">B11+B16</f>
-        <v>2711.24</v>
-      </c>
-      <c r="C17" s="34" t="n">
+        <v>2805.252</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <f aca="false">C11+C16</f>
-        <v>-63.76</v>
+        <v>-37.248</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="A18" s="32" t="s">
+        <v>105</v>
+      </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="32" t="n">
-        <f aca="false">-(前提!B18+MAX(0,前提!B19-B6))*前提!B13</f>
+      <c r="A19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="33" t="n">
+        <f aca="false">-(前提!B19+MAX(0,前提!B20-B6))*前提!B13</f>
         <v>-360</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="36" t="n">
-        <f aca="false">B17+B19</f>
-        <v>2351.24</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <f aca="false">C17+C19</f>
-        <v>-63.76</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="38" t="n">
-        <f aca="false">前提!D9*(1+前提!B12)^5*0.25/5-前提!D9*0.25/5</f>
+      <c r="A20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="33" t="n">
+        <f aca="false">前提!D9*前提!B21*前提!B22*前提!B23</f>
+        <v>50</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <f aca="false">前提!D9*前提!B21*前提!B22*前提!B23</f>
+        <v>50</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="37" t="n">
+        <f aca="false">B17+B19+B20</f>
+        <v>2495.252</v>
+      </c>
+      <c r="C21" s="37" t="n">
+        <f aca="false">C17+C19+C20</f>
+        <v>12.752</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="38" t="n">
+        <f aca="false">前提!D9*((1+前提!B12)^5-1)*前提!B18/5</f>
         <v>169.1127888</v>
       </c>
-      <c r="C22" s="38" t="n">
-        <f aca="false">前提!D9*((1+前提!B12)^5-1)*前提!B17/5</f>
+      <c r="C23" s="38" t="n">
+        <f aca="false">前提!D9*((1+前提!B12)^5-1)*前提!B18/5</f>
         <v>169.1127888</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="36" t="n">
-        <f aca="false">B20+B22</f>
-        <v>2520.3527888</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <f aca="false">C20+C22</f>
-        <v>105.3527888</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="E23" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="37" t="n">
+        <f aca="false">B21+B23</f>
+        <v>2664.3647888</v>
+      </c>
+      <c r="C24" s="37" t="n">
+        <f aca="false">C21+C23</f>
+        <v>181.8647888</v>
+      </c>
+      <c r="E24" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="40" t="n">
-        <f aca="false">(前提!D9*前提!B16-前提!D9*前提!B14)/マイル計算!D9</f>
-        <v>0.271739130434783</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>100</v>
+      <c r="A26" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="41" t="n">
-        <f aca="false">マイル計算!D19</f>
-        <v>0.445</v>
+      <c r="A27" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="39" t="n">
+        <f aca="false">(C7+C14+C20)/マイル計算!D9</f>
+        <v>0.466507177033493</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="42" t="str">
-        <f aca="false">IF(B27&lt;=B26,"OK：ストックのみで黒字","要改善：ストックのみでは赤字")</f>
-        <v>要改善：ストックのみでは赤字</v>
+      <c r="A28" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <f aca="false">マイル計算!D21</f>
+        <v>0.436</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="40" t="str">
+        <f aca="false">IF(B28&lt;=B27,"OK：ストックのみで黒字","要改善：ストックのみでは赤字")</f>
+        <v>OK：ストックのみで黒字</v>
       </c>
     </row>
   </sheetData>
